--- a/Figure 1/Figure 1B.xlsx
+++ b/Figure 1/Figure 1B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF25AFA-23F6-4A03-A12B-8807CA14D892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C5604C-852A-42C1-A801-F55585F7F4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +139,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,13 +167,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -455,200 +462,200 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>12.54</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>11.96</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>12.32</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>12.15</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>10.25</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>10.68</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>10.47</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>10.28</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>11.02</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>12.03</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>12.41</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>11.67</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>14.52</v>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>15.21</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>14.89</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>12.12</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>11.49</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>11.35</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>11.15</v>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>10.95</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>11.24</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
